--- a/FCyI/Armenia_data.xlsx
+++ b/FCyI/Armenia_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoryerz/Desktop/GaR-project/FCyI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E2B05B-4BC7-E64E-AF69-804331581681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDD06BC-E603-8C46-9630-4FB914AE4634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -376,10 +376,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -3141,38 +3141,6 @@
       </c>
       <c r="J86">
         <v>0.22093023359775543</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A87" s="1">
-        <v>45473</v>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87">
-        <v>0.8139534592628479</v>
-      </c>
-      <c r="D87">
-        <v>1.1627906933426857E-2</v>
-      </c>
-      <c r="E87">
-        <v>0.86046510934829712</v>
-      </c>
-      <c r="F87">
-        <v>0.23255814611911774</v>
-      </c>
-      <c r="G87">
-        <v>0.13953489065170288</v>
-      </c>
-      <c r="H87">
-        <v>1.1627906933426857E-2</v>
-      </c>
-      <c r="I87">
-        <v>0.46511629223823547</v>
-      </c>
-      <c r="J87">
-        <v>0.25581395626068115</v>
       </c>
     </row>
   </sheetData>
